--- a/marketing_forms/005_event_programming_form--marketing_forms.xlsx
+++ b/marketing_forms/005_event_programming_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>terms</t>
+          <t>Event Programming Form 19 Terms</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Event Programming Form 20 Notes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Event Programming Form 21 Description</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Event Programming Form 22 Start Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>Event Programming Form 23 End Date</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Event Programming Form 24 Email</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Event Programming Form 25 Phone</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
